--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BARA\Documents\UiPath\UCL_Remider_Expire\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C121D6-28E7-452E-ACA4-10797B5581DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CF33A8-6304-4CBA-9120-B993BA4EDE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
   <si>
     <t>Name</t>
   </si>
@@ -212,6 +212,30 @@
 AND DATEDIFF(DAY, CAST(GETDATE() AS DATE), CAST(COMPANY_PROFILE_PERIOD_END AS DATE)) &lt;= $OFFSET$
 AND (COMPANY_NAME_TH &lt;&gt; N'UCL ZERO' or COMPANY_NAME_EN &lt;&gt; N'UCL ZERO')
 ORDER BY profile.COMPANY_PROFILE_PERIOD_END ASC</t>
+  </si>
+  <si>
+    <t>strTemplatePath_Reminder_Expire</t>
+  </si>
+  <si>
+    <t>strTemplatePath_Reminder_Expire_Not_found</t>
+  </si>
+  <si>
+    <t>Data\Temp\Reminder_Expire.docx</t>
+  </si>
+  <si>
+    <t>Data\Temp\Reminder_Expire_Not_found.docx</t>
+  </si>
+  <si>
+    <t>Data\Output</t>
+  </si>
+  <si>
+    <t>strProcessedResourceFilePath</t>
+  </si>
+  <si>
+    <t>strTemplateReplaceString_ExpireDataTable</t>
+  </si>
+  <si>
+    <t>&lt;$RDE_dt_Reminder_Expire_Report$&gt;</t>
   </si>
 </sst>
 </file>
@@ -599,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z973"/>
+  <dimension ref="A1:Z977"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="58.140625" style="4" customWidth="1"/>
@@ -681,21 +705,49 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="409.5">
+    <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="409.5">
+      <c r="A10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
@@ -1659,6 +1711,10 @@
     <row r="971" ht="14.25" customHeight="1"/>
     <row r="972" ht="14.25" customHeight="1"/>
     <row r="973" ht="14.25" customHeight="1"/>
+    <row r="974" ht="14.25" customHeight="1"/>
+    <row r="975" ht="14.25" customHeight="1"/>
+    <row r="976" ht="14.25" customHeight="1"/>
+    <row r="977" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BARA\Documents\UiPath\UCL_Remider_Expire\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CF33A8-6304-4CBA-9120-B993BA4EDE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25561494-B390-46AA-BE6B-B555DA4D59E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
   <si>
     <t>Name</t>
   </si>
@@ -237,12 +237,30 @@
   <si>
     <t>&lt;$RDE_dt_Reminder_Expire_Report$&gt;</t>
   </si>
+  <si>
+    <t>strMailSubject_Report</t>
+  </si>
+  <si>
+    <t>strMailSubject_NoReport</t>
+  </si>
+  <si>
+    <t>Test Report</t>
+  </si>
+  <si>
+    <t>Test Not found</t>
+  </si>
+  <si>
+    <t>strMailSendTo</t>
+  </si>
+  <si>
+    <t>Aphiruth.s@baraadv.co.th</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -266,6 +284,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -284,10 +308,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -309,8 +334,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -623,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z977"/>
+  <dimension ref="A1:Z980"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="58.140625" style="4" customWidth="1"/>
@@ -737,20 +766,41 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="409.5">
+    <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="409.5">
+      <c r="A13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C13" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
@@ -1715,10 +1765,16 @@
     <row r="975" ht="14.25" customHeight="1"/>
     <row r="976" ht="14.25" customHeight="1"/>
     <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="B12" r:id="rId1" xr:uid="{F0564C91-B156-493F-A907-F75E6406DBB7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2969,8 +3025,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A3" s="4"/>
+    </row>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A4" s="4"/>
+    </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BARA\Documents\UiPath\UCL_Remider_Expire\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25561494-B390-46AA-BE6B-B555DA4D59E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C88EBCD-8704-4692-8E34-C59D0CBBD4FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="78">
   <si>
     <t>Name</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>Description (Assets will always overwrite other config)</t>
-  </si>
-  <si>
-    <t>MaxRetryNumber</t>
   </si>
   <si>
     <t>ExScreenshotsFolderPath</t>
@@ -107,9 +104,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Must be 0 if working with Orchestrator queues. If &gt; 0, the robot will retry the same transaction which failed with a system exception. Must be an integer value.</t>
-  </si>
-  <si>
     <t>Static part of logging message. Processed Transaction succesful.</t>
   </si>
   <si>
@@ -198,8 +192,106 @@
 $OFFSET$ = days before they expired to notify.</t>
   </si>
   <si>
+    <t>strTemplatePath_Reminder_Expire</t>
+  </si>
+  <si>
+    <t>strTemplatePath_Reminder_Expire_Not_found</t>
+  </si>
+  <si>
+    <t>Data\Temp\Reminder_Expire.docx</t>
+  </si>
+  <si>
+    <t>Data\Temp\Reminder_Expire_Not_found.docx</t>
+  </si>
+  <si>
+    <t>Data\Output</t>
+  </si>
+  <si>
+    <t>strProcessedResourceFilePath</t>
+  </si>
+  <si>
+    <t>strTemplateReplaceString_ExpireDataTable</t>
+  </si>
+  <si>
+    <t>&lt;$RDE_dt_Reminder_Expire_Report$&gt;</t>
+  </si>
+  <si>
+    <t>strMailSubject_Report</t>
+  </si>
+  <si>
+    <t>strMailSubject_NoReport</t>
+  </si>
+  <si>
+    <t>Test Report</t>
+  </si>
+  <si>
+    <t>Test Not found</t>
+  </si>
+  <si>
+    <t>strMailSendTo</t>
+  </si>
+  <si>
+    <t>Aphiruth.s@baraadv.co.th</t>
+  </si>
+  <si>
+    <t>strMailSubject_SystemError</t>
+  </si>
+  <si>
+    <t>strMailSubject_BusinessError</t>
+  </si>
+  <si>
+    <t>strMailSendTo_SystemError</t>
+  </si>
+  <si>
+    <t>strMailSendTo_BusinessError</t>
+  </si>
+  <si>
+    <t>Multiple email split by comma (,)</t>
+  </si>
+  <si>
+    <t>Expired Profile Reminder Prosess Error</t>
+  </si>
+  <si>
+    <t>Aphiruth.s@baraadv.co.th,korakrit.s@baraadv.co.th,</t>
+  </si>
+  <si>
+    <t>Expired Profile Reminder Prosess Business Error</t>
+  </si>
+  <si>
+    <t>_TEMP</t>
+  </si>
+  <si>
+    <t>strTemplateKeySubfix</t>
+  </si>
+  <si>
+    <t>strMailTableStyle</t>
+  </si>
+  <si>
+    <t>table {
+width: 100%;
+border-collapse: separate;
+border-spacing: 0;
+border: 1px solid #999;
+border-radius: 5px;
+overflow: hidden;
+}
+th {
+font-weight: bold;
+text-align: center;
+padding: 8px;
+background-color: #f2f2f2;
+border: 1px solid #ddd;
+}
+td {
+text-align: center;
+padding: 8px;
+border: 1px solid #ddd;
+align-content: start;
+}</t>
+  </si>
+  <si>
     <t>SELECT DATEDIFF(DAY, CAST(GETDATE() AS DATE), CAST(COMPANY_PROFILE_PERIOD_END AS DATE)) as DAYS_UNTIL_END 
-,profile.COMPANY_PROFILE_PERIOD_END
+,FORMAT( profile.COMPANY_PROFILE_PERIOD_END,'d MMM yyyy') AS COMPANY_PROFILE_PERIOD_END
 ,CASE company.COMPANY_LANGUAGE_TYPE WHEN 'EN' THEN company.COMPANY_NAME_EN ELSE
 company.COMPANY_NAME_TH END AS COMPANY_NAME
 ,invent.INVENTORY_NAME
@@ -210,57 +302,15 @@
   WHERE [profile].DELETE_FLAG = 0 AND (RENEW_ID is NULL OR RENEW_ID = '')
 AND COMPANY_PROFILE_PERIOD_END IS NOT NULL
 AND DATEDIFF(DAY, CAST(GETDATE() AS DATE), CAST(COMPANY_PROFILE_PERIOD_END AS DATE)) &lt;= $OFFSET$
-AND (COMPANY_NAME_TH &lt;&gt; N'UCL ZERO' or COMPANY_NAME_EN &lt;&gt; N'UCL ZERO')
+AND (company.IS_OWNER_PROFILE IS NULL OR company.IS_OWNER_PROFILE = 0)
 ORDER BY profile.COMPANY_PROFILE_PERIOD_END ASC</t>
-  </si>
-  <si>
-    <t>strTemplatePath_Reminder_Expire</t>
-  </si>
-  <si>
-    <t>strTemplatePath_Reminder_Expire_Not_found</t>
-  </si>
-  <si>
-    <t>Data\Temp\Reminder_Expire.docx</t>
-  </si>
-  <si>
-    <t>Data\Temp\Reminder_Expire_Not_found.docx</t>
-  </si>
-  <si>
-    <t>Data\Output</t>
-  </si>
-  <si>
-    <t>strProcessedResourceFilePath</t>
-  </si>
-  <si>
-    <t>strTemplateReplaceString_ExpireDataTable</t>
-  </si>
-  <si>
-    <t>&lt;$RDE_dt_Reminder_Expire_Report$&gt;</t>
-  </si>
-  <si>
-    <t>strMailSubject_Report</t>
-  </si>
-  <si>
-    <t>strMailSubject_NoReport</t>
-  </si>
-  <si>
-    <t>Test Report</t>
-  </si>
-  <si>
-    <t>Test Not found</t>
-  </si>
-  <si>
-    <t>strMailSendTo</t>
-  </si>
-  <si>
-    <t>Aphiruth.s@baraadv.co.th</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -290,6 +340,11 @@
       <color theme="10"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -312,7 +367,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -336,6 +391,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -652,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z980"/>
+  <dimension ref="A1:Z986"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="58.140625" style="4" customWidth="1"/>
@@ -698,128 +756,179 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4">
+    <row r="5" spans="1:26">
+      <c r="A5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="4">
         <v>60</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>45</v>
+      <c r="C5" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A15" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B15" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>67</v>
       </c>
+      <c r="B16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="13" spans="1:26" ht="409.5">
-      <c r="A13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>52</v>
+    <row r="17" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" ht="14.25" customHeight="1"/>
-    <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="18" spans="1:3" ht="315">
+      <c r="A18" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="409.5">
+      <c r="A19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="22" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="23" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="24" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="25" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="26" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="27" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -1768,19 +1877,27 @@
     <row r="978" ht="14.25" customHeight="1"/>
     <row r="979" ht="14.25" customHeight="1"/>
     <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="B12" r:id="rId1" xr:uid="{F0564C91-B156-493F-A907-F75E6406DBB7}"/>
+    <hyperlink ref="B13" r:id="rId1" xr:uid="{F0564C91-B156-493F-A907-F75E6406DBB7}"/>
+    <hyperlink ref="B16" r:id="rId2" xr:uid="{1CB6BA4B-5780-47B7-8EAD-3BF281ED260F}"/>
+    <hyperlink ref="B17" r:id="rId3" xr:uid="{9089DD37-D27C-43DB-96D8-363F3C3D3DC7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z991"/>
+  <dimension ref="A1:Z990"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -1823,173 +1940,163 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="30">
+    <row r="2" spans="1:26" ht="45">
       <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>23</v>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>37</v>
+    <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
-      <c r="C16" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A17" t="s">
-        <v>40</v>
+      <c r="A17" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A18" s="8" t="s">
-        <v>46</v>
+      <c r="A18" t="s">
+        <v>45</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="14.25" customHeight="1">
+    <row r="19" spans="1:3" ht="45">
       <c r="A19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
+        <v>34</v>
+      </c>
+      <c r="B19" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="45">
-      <c r="A20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" t="b">
-        <v>0</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
+    <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="22" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="23" spans="1:3" ht="14.25" customHeight="1"/>
@@ -2960,7 +3067,6 @@
     <row r="988" ht="14.25" customHeight="1"/>
     <row r="989" ht="14.25" customHeight="1"/>
     <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2986,7 +3092,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -3016,13 +3122,13 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BARA\Documents\UiPath\UCL_Remider_Expire\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C88EBCD-8704-4692-8E34-C59D0CBBD4FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7554066A-E2B6-4850-9D01-85688A862E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BARA\Documents\UiPath\UCL_Remider_Expire\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7554066A-E2B6-4850-9D01-85688A862E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEEC009F-194A-4C59-A94D-321A5A63CBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -304,6 +304,9 @@
 AND DATEDIFF(DAY, CAST(GETDATE() AS DATE), CAST(COMPANY_PROFILE_PERIOD_END AS DATE)) &lt;= $OFFSET$
 AND (company.IS_OWNER_PROFILE IS NULL OR company.IS_OWNER_PROFILE = 0)
 ORDER BY profile.COMPANY_PROFILE_PERIOD_END ASC</t>
+  </si>
+  <si>
+    <t>Non Production/Invoice_Storing</t>
   </si>
 </sst>
 </file>
@@ -759,7 +762,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BARA\Documents\UiPath\UCL_Remider_Expire\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEEC009F-194A-4C59-A94D-321A5A63CBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE48B10-2C80-4F24-AA4B-0D5B85119E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="78">
   <si>
     <t>Name</t>
   </si>
@@ -153,9 +153,6 @@
   </si>
   <si>
     <t>RetryNumberAddTransactionItem</t>
-  </si>
-  <si>
-    <t>Non Production/UCL/UCL_SignedInvoiceStoring</t>
   </si>
   <si>
     <t>LogMessage_TryToGetNewLocalFile</t>
@@ -762,15 +759,15 @@
         <v>26</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -786,137 +783,137 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="4">
         <v>60</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
       <c r="A17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="315">
       <c r="A18" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="409.5">
       <c r="A19" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
@@ -2013,10 +2010,10 @@
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
         <v>40</v>
-      </c>
-      <c r="B10" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
@@ -2074,7 +2071,7 @@
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -2082,7 +2079,7 @@
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -3082,7 +3079,7 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="43.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="60.28515625" customWidth="1"/>
     <col min="4" max="26" width="65.42578125" customWidth="1"/>
   </cols>
@@ -3125,31 +3122,156 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A3" s="4"/>
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A4" s="4"/>
-    </row>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
+      <c r="A4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BARA\Documents\UiPath\UCL_Remider_Expire\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE48B10-2C80-4F24-AA4B-0D5B85119E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC95632-F332-43F2-AE9E-F79E9F6E1609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="77">
   <si>
     <t>Name</t>
   </si>
@@ -185,10 +185,6 @@
     <t>RDE_strDayOfExpire</t>
   </si>
   <si>
-    <t>Parameter
-$OFFSET$ = days before they expired to notify.</t>
-  </si>
-  <si>
     <t>strTemplatePath_Reminder_Expire</t>
   </si>
   <si>
@@ -228,9 +224,6 @@
     <t>strMailSendTo</t>
   </si>
   <si>
-    <t>Aphiruth.s@baraadv.co.th</t>
-  </si>
-  <si>
     <t>strMailSubject_SystemError</t>
   </si>
   <si>
@@ -247,9 +240,6 @@
   </si>
   <si>
     <t>Expired Profile Reminder Prosess Error</t>
-  </si>
-  <si>
-    <t>Aphiruth.s@baraadv.co.th,korakrit.s@baraadv.co.th,</t>
   </si>
   <si>
     <t>Expired Profile Reminder Prosess Business Error</t>
@@ -303,7 +293,14 @@
 ORDER BY profile.COMPANY_PROFILE_PERIOD_END ASC</t>
   </si>
   <si>
-    <t>Non Production/Invoice_Storing</t>
+    <t>Production/UCL_Remider_Expire</t>
+  </si>
+  <si>
+    <t>Parameter
+$OFFSET$ = days before they expired to notify.(int_RDE_DayOfExpire)</t>
+  </si>
+  <si>
+    <t>uipathsupport@baraadv.co.th</t>
   </si>
 </sst>
 </file>
@@ -759,15 +756,15 @@
         <v>26</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -802,107 +799,107 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="315">
       <c r="A18" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="409.5">
@@ -910,10 +907,10 @@
         <v>45</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
@@ -1885,13 +1882,8 @@
     <row r="986" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <hyperlinks>
-    <hyperlink ref="B13" r:id="rId1" xr:uid="{F0564C91-B156-493F-A907-F75E6406DBB7}"/>
-    <hyperlink ref="B16" r:id="rId2" xr:uid="{1CB6BA4B-5780-47B7-8EAD-3BF281ED260F}"/>
-    <hyperlink ref="B17" r:id="rId3" xr:uid="{9089DD37-D27C-43DB-96D8-363F3C3D3DC7}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3097,7 +3089,9 @@
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -3128,7 +3122,11 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="E2">
+        <f>_xlfn.XLOOKUP(A2,Settings!A:A,Settings!B:B,"",0,1)</f>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
@@ -3139,137 +3137,185 @@
         <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="E3" t="str">
+        <f>_xlfn.XLOOKUP(A3,Settings!A:A,Settings!B:B,"",0,1)</f>
+        <v>UCLPMS_ConnectionString</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="E4" t="str">
+        <f>_xlfn.XLOOKUP(A4,Settings!A:A,Settings!B:B,"",0,1)</f>
+        <v>&lt;$RDE_dt_Reminder_Expire_Report$&gt;</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="E5" t="str">
+        <f>_xlfn.XLOOKUP(A5,Settings!A:A,Settings!B:B,"",0,1)</f>
+        <v>Data\Temp\Reminder_Expire.docx</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="E6" t="str">
+        <f>_xlfn.XLOOKUP(A6,Settings!A:A,Settings!B:B,"",0,1)</f>
+        <v>Data\Temp\Reminder_Expire_Not_found.docx</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="E7" t="str">
+        <f>_xlfn.XLOOKUP(A7,Settings!A:A,Settings!B:B,"",0,1)</f>
+        <v>Data\Output</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="E8" t="str">
+        <f>_xlfn.XLOOKUP(A8,Settings!A:A,Settings!B:B,"",0,1)</f>
+        <v>Test Report</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="E9" t="str">
+        <f>_xlfn.XLOOKUP(A9,Settings!A:A,Settings!B:B,"",0,1)</f>
+        <v>Test Not found</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
+      </c>
+      <c r="E10" t="str">
+        <f>_xlfn.XLOOKUP(A10,Settings!A:A,Settings!B:B,"",0,1)</f>
+        <v>uipathsupport@baraadv.co.th</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="E11" t="str">
+        <f>_xlfn.XLOOKUP(A11,Settings!A:A,Settings!B:B,"",0,1)</f>
+        <v>Expired Profile Reminder Prosess Error</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="E12" t="str">
+        <f>_xlfn.XLOOKUP(A12,Settings!A:A,Settings!B:B,"",0,1)</f>
+        <v>Expired Profile Reminder Prosess Business Error</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>68</v>
+      <c r="E13" t="str">
+        <f>_xlfn.XLOOKUP(A13,Settings!A:A,Settings!B:B,"",0,1)</f>
+        <v>uipathsupport@baraadv.co.th</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
+      </c>
+      <c r="E14" t="str">
+        <f>_xlfn.XLOOKUP(A14,Settings!A:A,Settings!B:B,"",0,1)</f>
+        <v>uipathsupport@baraadv.co.th</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
